--- a/action/actionList_appCore.xlsx
+++ b/action/actionList_appCore.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\action\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F51B0F02-031F-41EC-9343-0520D732FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685C1184-DEC5-4FB7-B9B7-8A7B83C891CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Azioni" sheetId="1" r:id="rId1"/>
     <sheet name="Parametri azioni" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="594">
   <si>
     <t>Codice</t>
   </si>
@@ -1820,6 +1819,18 @@
   </si>
   <si>
     <t>Finestra  Principale</t>
+  </si>
+  <si>
+    <t>YAX3MVXP</t>
+  </si>
+  <si>
+    <t>Picking List</t>
+  </si>
+  <si>
+    <t>Picking List (YAX3MVXP)</t>
+  </si>
+  <si>
+    <t>Azioni (divise per funzionalità) (Az.Campo-az.bottone Finestra)</t>
   </si>
 </sst>
 </file>
@@ -1849,7 +1860,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1877,6 +1888,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2152,7 +2169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2300,6 +2317,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2581,7 +2604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O139"/>
+  <dimension ref="A1:O151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" customWidth="1"/>
@@ -3049,207 +3072,183 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="24" t="s">
         <v>585</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B14" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="12" t="s">
+      <c r="C14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E14" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H14" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="12" t="s">
+      <c r="I14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="K13" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
+      <c r="K14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="50" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56"/>
+      <c r="L15" s="56"/>
+      <c r="M15" s="56"/>
+    </row>
+    <row r="16" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="57" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="50" t="s">
         <v>578</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="35"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="B17" s="49"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="35"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B18" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="C18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" s="9" t="s">
+      <c r="H18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="9" t="s">
+      <c r="J18" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" s="4" t="s">
+      <c r="L18" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>511</v>
+        <v>60</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>23</v>
@@ -3270,13 +3269,13 @@
         <v>15</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>23</v>
@@ -3287,10 +3286,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>23</v>
@@ -3317,7 +3316,7 @@
         <v>15</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>23</v>
@@ -3331,10 +3330,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>65</v>
+        <v>511</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>23</v>
@@ -3355,13 +3354,13 @@
         <v>15</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>23</v>
@@ -3372,10 +3371,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>512</v>
+        <v>61</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>23</v>
@@ -3396,13 +3395,13 @@
         <v>15</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>23</v>
@@ -3416,10 +3415,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>23</v>
@@ -3446,7 +3445,7 @@
         <v>15</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>23</v>
@@ -3458,10 +3457,10 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>344</v>
+        <v>512</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>23</v>
@@ -3482,13 +3481,13 @@
         <v>15</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>23</v>
@@ -3499,13 +3498,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>551</v>
+        <v>62</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>558</v>
+        <v>348</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>331</v>
@@ -3529,218 +3528,218 @@
         <v>15</v>
       </c>
       <c r="K25" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>551</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="L25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="24" t="s">
+      <c r="L27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B28" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="C28" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E28" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G28" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" s="12" t="s">
+      <c r="H28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J26" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K26" s="12" t="s">
+      <c r="J28" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="L26" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M26" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
+      <c r="L28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="O29" s="5"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
         <v>580</v>
       </c>
-      <c r="B28" s="51"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="35"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="B30" s="51"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="35"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B31" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="9" t="s">
+      <c r="C31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F31" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G31" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="9" t="s">
+      <c r="H31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J29" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" s="9" t="s">
+      <c r="J31" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="L29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="O29" s="5"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J30" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M31" s="4" t="s">
+      <c r="L31" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>513</v>
+        <v>84</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>23</v>
@@ -3761,13 +3760,13 @@
         <v>15</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>23</v>
@@ -3779,10 +3778,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>23</v>
@@ -3809,7 +3808,7 @@
         <v>15</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>23</v>
@@ -3820,10 +3819,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>87</v>
+        <v>513</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>23</v>
@@ -3844,13 +3843,13 @@
         <v>15</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>23</v>
@@ -3862,10 +3861,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>514</v>
+        <v>86</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>23</v>
@@ -3886,13 +3885,13 @@
         <v>15</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>23</v>
@@ -3906,10 +3905,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>23</v>
@@ -3936,7 +3935,7 @@
         <v>15</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>23</v>
@@ -3948,10 +3947,10 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>23</v>
@@ -3978,7 +3977,7 @@
         <v>15</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>23</v>
@@ -3989,10 +3988,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>23</v>
@@ -4019,7 +4018,7 @@
         <v>15</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>23</v>
@@ -4030,13 +4029,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>552</v>
+        <v>515</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>559</v>
+        <v>359</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>331</v>
@@ -4054,226 +4053,226 @@
         <v>15</v>
       </c>
       <c r="I39" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J39" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K39" s="5" t="s">
+      <c r="J40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>559</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K41" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="L39" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M39" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="24" t="s">
+      <c r="L41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B42" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D40" s="12" t="s">
+      <c r="C42" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E42" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F42" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G40" s="12" t="s">
+      <c r="G42" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H40" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" s="12" t="s">
+      <c r="H42" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I42" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K40" s="12" t="s">
+      <c r="J42" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="L40" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="14" t="s">
+      <c r="L42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O42" s="5"/>
+    </row>
+    <row r="43" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="O43" s="5"/>
+    </row>
+    <row r="44" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
         <v>586</v>
       </c>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="35"/>
-      <c r="O42" s="5"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="35"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B45" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="C43" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" s="9" t="s">
+      <c r="C45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E45" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F45" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G45" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="9" t="s">
+      <c r="H45" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I45" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K43" s="9" t="s">
+      <c r="J45" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="L43" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="O43" s="5"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="L44" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" s="4" t="s">
+      <c r="L45" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="10" t="s">
         <v>15</v>
       </c>
       <c r="O45" s="5"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>23</v>
@@ -4300,7 +4299,7 @@
         <v>15</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>23</v>
@@ -4311,10 +4310,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>516</v>
+        <v>112</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>23</v>
@@ -4335,13 +4334,13 @@
         <v>15</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="L47" s="5" t="s">
         <v>23</v>
@@ -4352,10 +4351,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>23</v>
@@ -4382,7 +4381,7 @@
         <v>15</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>23</v>
@@ -4393,10 +4392,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>23</v>
@@ -4417,13 +4416,13 @@
         <v>15</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>23</v>
@@ -4434,10 +4433,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>23</v>
@@ -4464,7 +4463,7 @@
         <v>15</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>23</v>
@@ -4475,10 +4474,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>23</v>
@@ -4499,13 +4498,13 @@
         <v>15</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>23</v>
@@ -4516,10 +4515,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>23</v>
@@ -4546,7 +4545,7 @@
         <v>15</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>23</v>
@@ -4557,10 +4556,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>108</v>
+        <v>518</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>23</v>
@@ -4581,13 +4580,13 @@
         <v>15</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>23</v>
@@ -4598,10 +4597,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>23</v>
@@ -4628,7 +4627,7 @@
         <v>15</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>23</v>
@@ -4639,10 +4638,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>23</v>
@@ -4669,7 +4668,7 @@
         <v>15</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>23</v>
@@ -4681,13 +4680,13 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>561</v>
+        <v>109</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>560</v>
+        <v>373</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>331</v>
@@ -4711,7 +4710,7 @@
         <v>15</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>561</v>
+        <v>109</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>23</v>
@@ -4722,13 +4721,13 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="19" t="s">
-        <v>562</v>
+        <v>110</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>563</v>
+        <v>374</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>331</v>
@@ -4752,217 +4751,217 @@
         <v>15</v>
       </c>
       <c r="K57" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="L58" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="19" t="s">
         <v>562</v>
       </c>
-      <c r="L57" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="24" t="s">
+      <c r="B59" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B60" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="C58" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="12" t="s">
+      <c r="C60" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E60" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="F60" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G60" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H58" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" s="12" t="s">
+      <c r="H60" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="J58" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K58" s="12" t="s">
+      <c r="J60" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="L58" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M58" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="5"/>
-      <c r="M59" s="5"/>
-    </row>
-    <row r="60" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="14" t="s">
+      <c r="L60" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+    </row>
+    <row r="62" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="35"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="18" t="s">
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="34"/>
+      <c r="M62" s="35"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B63" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D61" s="9" t="s">
+      <c r="C63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E61" s="9" t="s">
+      <c r="E63" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="9" t="s">
+      <c r="F63" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G63" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H61" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" s="9" t="s">
+      <c r="H63" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J61" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" s="9" t="s">
+      <c r="J63" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="L61" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K62" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L62" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J63" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="L63" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M63" s="4" t="s">
+      <c r="L63" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M63" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>23</v>
@@ -4983,13 +4982,13 @@
         <v>15</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>23</v>
@@ -5000,10 +4999,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>23</v>
@@ -5024,13 +5023,13 @@
         <v>15</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>23</v>
@@ -5041,13 +5040,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>331</v>
@@ -5071,7 +5070,7 @@
         <v>15</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>23</v>
@@ -5080,203 +5079,211 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" s="12" t="s">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G67" s="12" t="s">
+      <c r="G67" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H67" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K67" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="L67" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M67" s="13" t="s">
+      <c r="H67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="O67" s="5" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="69" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K69" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="L69" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M69" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+    </row>
+    <row r="71" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="14" t="s">
         <v>528</v>
       </c>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
-      <c r="G69" s="34"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="34"/>
-      <c r="J69" s="34"/>
-      <c r="K69" s="34"/>
-      <c r="L69" s="34"/>
-      <c r="M69" s="35"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="18" t="s">
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="35"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A72" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B72" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D70" s="9" t="s">
+      <c r="C72" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E70" s="9" t="s">
+      <c r="E72" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F70" s="9" t="s">
+      <c r="F72" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="G72" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H70" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" s="9" t="s">
+      <c r="H72" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="J70" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K70" s="9" t="s">
+      <c r="J72" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K72" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="L70" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M70" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="31" t="s">
+      <c r="L72" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A73" s="31" t="s">
         <v>549</v>
       </c>
-      <c r="B71" s="43" t="s">
+      <c r="B73" s="43" t="s">
         <v>548</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="4"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A72" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G72" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J72" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L72" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A73" s="19" t="s">
-        <v>449</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>520</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>23</v>
@@ -5299,25 +5306,17 @@
       <c r="I73" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="J73" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" s="19" t="s">
-        <v>526</v>
-      </c>
-      <c r="L73" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M73" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="4"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="19" t="s">
-        <v>519</v>
+        <v>137</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>521</v>
+        <v>385</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>23</v>
@@ -5355,10 +5354,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="19" t="s">
-        <v>522</v>
+        <v>449</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>23</v>
@@ -5384,8 +5383,8 @@
       <c r="J75" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K75" s="5" t="s">
-        <v>527</v>
+      <c r="K75" s="19" t="s">
+        <v>526</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>23</v>
@@ -5396,10 +5395,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="19" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>23</v>
@@ -5437,10 +5436,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="19" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>23</v>
@@ -5466,8 +5465,8 @@
       <c r="J77" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K77" s="19" t="s">
-        <v>533</v>
+      <c r="K77" s="5" t="s">
+        <v>527</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>23</v>
@@ -5478,10 +5477,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="19" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>23</v>
@@ -5519,10 +5518,10 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="19" t="s">
-        <v>156</v>
+        <v>529</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>158</v>
+        <v>530</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>23</v>
@@ -5548,8 +5547,8 @@
       <c r="J79" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K79" s="5" t="s">
-        <v>159</v>
+      <c r="K79" s="19" t="s">
+        <v>533</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>23</v>
@@ -5560,10 +5559,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
-        <v>386</v>
+        <v>532</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>160</v>
+        <v>531</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>23</v>
@@ -5584,13 +5583,13 @@
         <v>15</v>
       </c>
       <c r="I80" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>161</v>
+        <v>66</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>23</v>
@@ -5601,22 +5600,22 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="19" t="s">
-        <v>387</v>
+        <v>156</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>15</v>
+        <v>331</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="G81" s="5" t="s">
         <v>12</v>
@@ -5625,27 +5624,27 @@
         <v>15</v>
       </c>
       <c r="I81" s="5" t="s">
-        <v>164</v>
+        <v>550</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>15</v>
+        <v>159</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M81" s="4" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="19" t="s">
-        <v>534</v>
+        <v>386</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>535</v>
+        <v>160</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>23</v>
@@ -5666,13 +5665,13 @@
         <v>15</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>550</v>
+        <v>68</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>536</v>
+        <v>161</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>23</v>
@@ -5683,22 +5682,22 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="19" t="s">
-        <v>537</v>
+        <v>387</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>538</v>
+        <v>162</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>331</v>
+        <v>15</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>24</v>
+        <v>163</v>
       </c>
       <c r="G83" s="5" t="s">
         <v>12</v>
@@ -5707,27 +5706,27 @@
         <v>15</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>550</v>
+        <v>164</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>539</v>
+        <v>15</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="19" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>23</v>
@@ -5754,7 +5753,7 @@
         <v>15</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>23</v>
@@ -5765,10 +5764,10 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="19" t="s">
-        <v>166</v>
+        <v>537</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>388</v>
+        <v>538</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>23</v>
@@ -5795,7 +5794,7 @@
         <v>15</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>167</v>
+        <v>539</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>23</v>
@@ -5806,10 +5805,10 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="19" t="s">
-        <v>168</v>
+        <v>540</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>389</v>
+        <v>541</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>23</v>
@@ -5836,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>170</v>
+        <v>542</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>23</v>
@@ -5847,10 +5846,10 @@
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="19" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>23</v>
@@ -5877,7 +5876,7 @@
         <v>15</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>23</v>
@@ -5887,14 +5886,14 @@
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="31" t="s">
-        <v>553</v>
-      </c>
-      <c r="B88" s="43" t="s">
-        <v>554</v>
+      <c r="A88" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>389</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>331</v>
@@ -5918,413 +5917,413 @@
         <v>15</v>
       </c>
       <c r="K88" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="L89" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="B90" s="43" t="s">
+        <v>554</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="L88" s="5" t="s">
+      <c r="L90" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="M88" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="24" t="s">
+      <c r="M90" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B91" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" s="12" t="s">
+      <c r="C91" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E91" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F89" s="12" t="s">
+      <c r="F91" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G89" s="12" t="s">
+      <c r="G91" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H89" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I89" s="12" t="s">
+      <c r="H91" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="J89" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K89" s="12" t="s">
+      <c r="J91" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K91" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="L89" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M89" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
-      <c r="J90" s="5"/>
-      <c r="K90" s="5"/>
-      <c r="L90" s="5"/>
-      <c r="M90" s="5"/>
-    </row>
-    <row r="91" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="14" t="s">
+      <c r="L91" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M91" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+      <c r="K92" s="5"/>
+      <c r="L92" s="5"/>
+      <c r="M92" s="5"/>
+    </row>
+    <row r="93" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B91" s="34"/>
-      <c r="C91" s="34"/>
-      <c r="D91" s="34"/>
-      <c r="E91" s="34"/>
-      <c r="F91" s="34"/>
-      <c r="G91" s="34"/>
-      <c r="H91" s="34"/>
-      <c r="I91" s="34"/>
-      <c r="J91" s="34"/>
-      <c r="K91" s="34"/>
-      <c r="L91" s="34"/>
-      <c r="M91" s="35"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A92" s="18" t="s">
+      <c r="B93" s="34"/>
+      <c r="C93" s="34"/>
+      <c r="D93" s="34"/>
+      <c r="E93" s="34"/>
+      <c r="F93" s="34"/>
+      <c r="G93" s="34"/>
+      <c r="H93" s="34"/>
+      <c r="I93" s="34"/>
+      <c r="J93" s="34"/>
+      <c r="K93" s="34"/>
+      <c r="L93" s="34"/>
+      <c r="M93" s="35"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B94" s="9" t="s">
         <v>543</v>
       </c>
-      <c r="C92" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" s="9" t="s">
+      <c r="C94" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E92" s="9" t="s">
+      <c r="E94" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F92" s="9" t="s">
+      <c r="F94" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G92" s="9" t="s">
+      <c r="G94" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H92" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I92" s="9" t="s">
+      <c r="H94" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J92" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K92" s="9" t="s">
+      <c r="J94" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K94" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="L92" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M92" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="19" t="s">
+      <c r="L94" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M94" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="19" t="s">
         <v>477</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B95" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="C93" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D93" s="5" t="s">
+      <c r="C95" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E93" s="5" t="s">
+      <c r="E95" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F93" s="5" t="s">
+      <c r="F95" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G95" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H93" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" s="5" t="s">
+      <c r="H95" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="J93" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K93" s="5" t="s">
+      <c r="J95" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K95" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="L93" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M93" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A94" s="19" t="s">
+      <c r="L95" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B96" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="C94" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D94" s="5" t="s">
+      <c r="C96" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="E94" s="5" t="s">
+      <c r="E96" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F94" s="5" t="s">
+      <c r="F96" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G96" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H94" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I94" s="5" t="s">
+      <c r="H96" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="J94" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K94" s="5" t="s">
+      <c r="J96" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="L94" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M94" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="24" t="s">
+      <c r="L96" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B97" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C95" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D95" s="12" t="s">
+      <c r="C97" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E97" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F95" s="12" t="s">
+      <c r="F97" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G95" s="12" t="s">
+      <c r="G97" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H95" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I95" s="12" t="s">
+      <c r="H97" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="J95" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K95" s="11" t="s">
+      <c r="J97" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K97" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="L95" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M95" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="5"/>
-      <c r="M96" s="5"/>
-    </row>
-    <row r="97" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
+      <c r="L97" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M97" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="M98" s="5"/>
+    </row>
+    <row r="99" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B97" s="34"/>
-      <c r="C97" s="34"/>
-      <c r="D97" s="34"/>
-      <c r="E97" s="34"/>
-      <c r="F97" s="34"/>
-      <c r="G97" s="34"/>
-      <c r="H97" s="34"/>
-      <c r="I97" s="34"/>
-      <c r="J97" s="34"/>
-      <c r="K97" s="34"/>
-      <c r="L97" s="34"/>
-      <c r="M97" s="35"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="18" t="s">
+      <c r="B99" s="34"/>
+      <c r="C99" s="34"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="34"/>
+      <c r="F99" s="34"/>
+      <c r="G99" s="34"/>
+      <c r="H99" s="34"/>
+      <c r="I99" s="34"/>
+      <c r="J99" s="34"/>
+      <c r="K99" s="34"/>
+      <c r="L99" s="34"/>
+      <c r="M99" s="35"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B100" s="9" t="s">
         <v>392</v>
       </c>
-      <c r="C98" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D98" s="9" t="s">
+      <c r="C100" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E98" s="9" t="s">
+      <c r="E100" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F98" s="9" t="s">
+      <c r="F100" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="G100" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H98" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I98" s="9" t="s">
+      <c r="H100" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="J98" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K98" s="9" t="s">
+      <c r="J100" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K100" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="L98" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M98" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A99" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G99" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H99" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J99" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K99" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="L99" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M99" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A100" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K100" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="L100" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M100" s="4" t="s">
+      <c r="L100" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M100" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="19" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>201</v>
+        <v>393</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>23</v>
@@ -6351,7 +6350,7 @@
         <v>15</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>23</v>
@@ -6362,10 +6361,10 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>23</v>
@@ -6392,7 +6391,7 @@
         <v>15</v>
       </c>
       <c r="K102" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>23</v>
@@ -6403,13 +6402,13 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="19" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>331</v>
@@ -6433,7 +6432,7 @@
         <v>15</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>23</v>
@@ -6444,13 +6443,13 @@
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="19" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>331</v>
@@ -6474,217 +6473,217 @@
         <v>15</v>
       </c>
       <c r="K104" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="L104" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K105" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="L105" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K106" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="L104" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M104" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="24" t="s">
+      <c r="L106" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B107" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D105" s="12" t="s">
+      <c r="C107" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E107" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F105" s="12" t="s">
+      <c r="F107" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G105" s="12" t="s">
+      <c r="G107" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H105" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I105" s="12" t="s">
+      <c r="H107" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I107" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J105" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K105" s="12" t="s">
+      <c r="J107" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K107" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="L105" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M105" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
-    </row>
-    <row r="107" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="14" t="s">
+      <c r="L107" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M107" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+    </row>
+    <row r="109" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B107" s="34"/>
-      <c r="C107" s="34"/>
-      <c r="D107" s="34"/>
-      <c r="E107" s="34"/>
-      <c r="F107" s="34"/>
-      <c r="G107" s="34"/>
-      <c r="H107" s="34"/>
-      <c r="I107" s="34"/>
-      <c r="J107" s="34"/>
-      <c r="K107" s="34"/>
-      <c r="L107" s="34"/>
-      <c r="M107" s="35"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="18" t="s">
+      <c r="B109" s="34"/>
+      <c r="C109" s="34"/>
+      <c r="D109" s="34"/>
+      <c r="E109" s="34"/>
+      <c r="F109" s="34"/>
+      <c r="G109" s="34"/>
+      <c r="H109" s="34"/>
+      <c r="I109" s="34"/>
+      <c r="J109" s="34"/>
+      <c r="K109" s="34"/>
+      <c r="L109" s="34"/>
+      <c r="M109" s="35"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B110" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C108" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D108" s="9" t="s">
+      <c r="C110" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D110" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="E108" s="9" t="s">
+      <c r="E110" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F108" s="9" t="s">
+      <c r="F110" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G108" s="9" t="s">
+      <c r="G110" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H108" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I108" s="9" t="s">
+      <c r="H110" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="J108" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K108" s="9" t="s">
+      <c r="J110" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="L108" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M108" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H109" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I109" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K109" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="L109" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M109" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A110" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H110" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I110" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="J110" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K110" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L110" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M110" s="4" t="s">
+      <c r="L110" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="M110" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="19" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>23</v>
@@ -6705,13 +6704,13 @@
         <v>15</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>224</v>
+        <v>66</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>23</v>
@@ -6722,10 +6721,10 @@
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="19" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>23</v>
@@ -6746,13 +6745,13 @@
         <v>15</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>23</v>
@@ -6763,10 +6762,10 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="19" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>23</v>
@@ -6787,27 +6786,27 @@
         <v>15</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K113" s="5" t="s">
-        <v>15</v>
+        <v>224</v>
       </c>
       <c r="L113" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>23</v>
@@ -6828,13 +6827,13 @@
         <v>15</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K114" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="L114" s="5" t="s">
         <v>23</v>
@@ -6845,10 +6844,10 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="19" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>23</v>
@@ -6869,27 +6868,27 @@
         <v>15</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="J115" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K115" s="5" t="s">
-        <v>234</v>
+        <v>15</v>
       </c>
       <c r="L115" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M115" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="19" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>23</v>
@@ -6910,27 +6909,27 @@
         <v>15</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="J116" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K116" s="5" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
       <c r="L116" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>23</v>
@@ -6951,13 +6950,13 @@
         <v>15</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="J117" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L117" s="5" t="s">
         <v>23</v>
@@ -6968,10 +6967,10 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>23</v>
@@ -6992,27 +6991,27 @@
         <v>15</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="J118" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K118" s="5" t="s">
-        <v>242</v>
+        <v>15</v>
       </c>
       <c r="L118" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="19" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>23</v>
@@ -7033,27 +7032,27 @@
         <v>15</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="J119" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K119" s="5" t="s">
-        <v>15</v>
+        <v>237</v>
       </c>
       <c r="L119" s="5" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="19" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>23</v>
@@ -7074,13 +7073,13 @@
         <v>15</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="J120" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="L120" s="5" t="s">
         <v>23</v>
@@ -7091,10 +7090,10 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>23</v>
@@ -7115,27 +7114,27 @@
         <v>15</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="J121" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>250</v>
+        <v>15</v>
       </c>
       <c r="L121" s="5" t="s">
-        <v>23</v>
+        <v>244</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="19" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>23</v>
@@ -7156,27 +7155,27 @@
         <v>15</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>15</v>
+        <v>247</v>
       </c>
       <c r="L122" s="5" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="M122" s="4" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="19" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>23</v>
@@ -7197,13 +7196,13 @@
         <v>15</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="J123" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K123" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>23</v>
@@ -7214,10 +7213,10 @@
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="19" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>23</v>
@@ -7238,27 +7237,27 @@
         <v>15</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="J124" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K124" s="5" t="s">
-        <v>257</v>
+        <v>15</v>
       </c>
       <c r="L124" s="5" t="s">
-        <v>23</v>
+        <v>244</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="19" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>23</v>
@@ -7279,13 +7278,13 @@
         <v>15</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="J125" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="L125" s="5" t="s">
         <v>23</v>
@@ -7296,10 +7295,10 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="19" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>23</v>
@@ -7320,28 +7319,30 @@
         <v>15</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K126" s="5" t="s">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="L126" s="5" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="M126" s="4" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="31" t="s">
-        <v>557</v>
-      </c>
-      <c r="B127" s="43"/>
+      <c r="A127" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>259</v>
+      </c>
       <c r="C127" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>331</v>
@@ -7359,131 +7360,217 @@
         <v>15</v>
       </c>
       <c r="I127" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K127" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="L127" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H128" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K128" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L128" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="M128" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="31" t="s">
+        <v>557</v>
+      </c>
+      <c r="B129" s="43"/>
+      <c r="C129" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I129" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J127" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K127" s="43"/>
-      <c r="L127" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M127" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="24" t="s">
+      <c r="J129" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K129" s="43"/>
+      <c r="L129" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M129" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B130" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="C128" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D128" s="12" t="s">
+      <c r="C130" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="E128" s="12" t="s">
+      <c r="E130" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F128" s="12" t="s">
+      <c r="F130" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G128" s="12" t="s">
+      <c r="G130" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="H128" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I128" s="12" t="s">
+      <c r="H130" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I130" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="J128" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K128" s="12" t="s">
+      <c r="J130" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K130" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="L128" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="M128" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="24"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="5"/>
-      <c r="M129" s="5"/>
-    </row>
-    <row r="130" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="14" t="s">
+      <c r="L130" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M130" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="24"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5"/>
+      <c r="L131" s="5"/>
+      <c r="M131" s="5"/>
+    </row>
+    <row r="132" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="B130" s="5"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A131" s="19" t="s">
+      <c r="B132" s="5"/>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B133" t="s">
         <v>317</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D131" s="5" t="s">
+      <c r="C133" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="E131" s="5" t="s">
+      <c r="E133" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F131" s="5" t="s">
+      <c r="F133" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G131" s="5" t="s">
+      <c r="G133" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H131" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I131" s="5" t="s">
+      <c r="H133" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I133" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="J131" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K131" s="5" t="s">
+      <c r="J133" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="K133" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="L131" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M131" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A132" s="19" t="s">
+      <c r="L133" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M133" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="19" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="139" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="46" t="s">
+    <row r="140" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="141" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="46" t="s">
         <v>579</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="151" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="46" t="s">
+        <v>592</v>
       </c>
     </row>
   </sheetData>
